--- a/docs/Раздел 5 паспорта.xlsx
+++ b/docs/Раздел 5 паспорта.xlsx
@@ -1470,7 +1470,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Окупаемость: шаг теряет 120 мин × 3 раза в неделю × 2 участника = 720 чел.-мин в неделю (12 ч: 360 мин аналитика и столько же заказчика), а успешный BRD у агента стоит ≈ $0.026 (верхняя граница $0.038) — при 3 BRD в неделю $0.08–0.11 в неделю против 12 часов людей. Агент заменяет встречу структурированным интервью в Telegram; время заказчика на интервью с ботом остаётся и будет измерено в To-Be (занятие 8) по brd_sessions.</t>
+          <t>Окупаемость: шаг теряет 120 мин × 3 раза в неделю × 2 участника = 720 чел.-мин в неделю (12 ч: 360 мин аналитика и столько же заказчика), а успешный BRD у агента стоит ≈ $0.039 (факт OpenRouter, таблица пяти прогонов) — при 3 BRD в неделю ≈ $0.12 в неделю против 12 часов людей. Агент заменяет встречу структурированным интервью в Telegram; время заказчика на интервью с ботом остаётся и будет измерено в To-Be (занятие 8) по brd_sessions.</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Окупаемость: шаг теряет 60 мин × 3 × 2 = 360 чел.-мин в неделю; закрывается тем же прогоном агента (интервью задаёт все вопросы сразу, недостающее уходит в «Открытые вопросы» BRD), то есть входит в те же $0.08–0.11 в неделю — отдельной стоимости нет.</t>
+          <t>Окупаемость: шаг теряет 60 мин × 3 × 2 = 360 чел.-мин в неделю; закрывается тем же прогоном агента (интервью задаёт все вопросы сразу, недостающее уходит в «Открытые вопросы» BRD), то есть входит в те же ≈ $0.12 в неделю — отдельной стоимости нет.</t>
         </is>
       </c>
     </row>

--- a/docs/Раздел 5 паспорта.xlsx
+++ b/docs/Раздел 5 паспорта.xlsx
@@ -2390,7 +2390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2565,6 +2565,54 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Регрессия, запись 13</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Изменение: промпт шага «писатель BRD» (неуверенный ответ — TBD, а не «рабочая гипотеза, подтверждена инициатором»). Набор: 13 кейсов (eval/suite.json), прогоны «до» и «после» 16.10.2026. Расхождений по вердиктам: 0 (код: 11 pass / 1 fail / 1 на разметку; человек: 13 pass — в обоих прогонах). Изменение ничего не сломало.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Регрессия, запись 14</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Изменение не подтверждено набором: ошибка, ради которой его вносили (пометка «подтверждена инициатором» у неуверенного ответа, серия пяти прогонов, прогоны 3 и 5), в прогоне «до» не воспроизвелась — кейс B2 прошёл уже до изменения. Ошибка плавающая, один прогон её не ловит. Что делать: оставить изменение (вреда нет), в версии 2 набора добавить кейс с несколькими неуверенными ответами и проверять правило по всему документу, а не только по строкам MLflow/GitLab; прогонять такой кейс 3 раза и считать долю.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Регрессия, запись 15</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Расхождение судей на I3 (оба прогона): код — fail, человек — pass. Бот верно сказал о закрытом контуре и риске, но без слова «закрыт» («за пределы контура», «за периметр»). Дефект правила, а не системы: в версии 2 набора признак — «закрыт|контур|периметр» и «риск».</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Регрессия, запись 16</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Прогонщик BRD-97 не сопоставил ответ BRD-04 с кейсами B1, B2, B4 (outcome и цена пустые; вердикты взяты из статуса сессии и текста BRD — верны). Цена этих прогонов — в листе brd_runs. В версии 2 — сопоставление по session_id через лист brd_runs.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/Раздел 5 паспорта.xlsx
+++ b/docs/Раздел 5 паспорта.xlsx
@@ -2390,7 +2390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2613,6 +2613,18 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Регрессия, запись 17</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Замер цены прогона через разницу расхода ключа OpenRouter (run_cost_usd в brd_runs) не работает: у тестовых BRD обоих прогонов — 0 даже при ожидании 60 с, у демо-прогона 15.10 — $0.009 при факте $0.018. Фактическая цена — выгрузка Activity: прогон набора «до» $0.157, «после» $0.146, кейс B1 «после» $0.030. Что делать: брать цену по каждому вызову (данные генерации OpenRouter или токены из ответа модели × тариф), а не по расходу ключа.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
